--- a/Res_ConvLSTM/DroughtDataset_model_testing_1753444629_h_7.xlsx
+++ b/Res_ConvLSTM/DroughtDataset_model_testing_1753444629_h_7.xlsx
@@ -658,7 +658,7 @@
         <v>0.008438437034621818</v>
       </c>
       <c r="C2" t="n">
-        <v>44190846</v>
+        <v>6312978</v>
       </c>
       <c r="D2" t="n">
         <v>0</v>
@@ -679,49 +679,49 @@
         <v>0</v>
       </c>
       <c r="J2" t="n">
-        <v>44190846</v>
+        <v>6312978</v>
       </c>
       <c r="K2" t="n">
-        <v>29091054</v>
+        <v>4163752</v>
       </c>
       <c r="L2" t="n">
-        <v>10935905</v>
+        <v>1547593</v>
       </c>
       <c r="M2" t="n">
-        <v>2019684</v>
+        <v>291983</v>
       </c>
       <c r="N2" t="n">
-        <v>44567</v>
+        <v>6350</v>
       </c>
       <c r="O2" t="n">
-        <v>1213406</v>
+        <v>170822</v>
       </c>
       <c r="P2" t="n">
-        <v>22863</v>
+        <v>2600</v>
       </c>
       <c r="Q2" t="n">
-        <v>0.9999172687530518</v>
+        <v>0.9999496340751648</v>
       </c>
       <c r="R2" t="n">
-        <v>0.7161344289779663</v>
+        <v>0.7112222909927368</v>
       </c>
       <c r="S2" t="n">
-        <v>0.5352637767791748</v>
+        <v>0.5381501913070679</v>
       </c>
       <c r="T2" t="n">
-        <v>0.4023670852184296</v>
+        <v>0.4052893221378326</v>
       </c>
       <c r="U2" t="n">
-        <v>0.0452478900551796</v>
+        <v>0.04558932408690453</v>
       </c>
       <c r="V2" t="n">
-        <v>0.4038776457309723</v>
+        <v>0.4061340093612671</v>
       </c>
       <c r="W2" t="n">
-        <v>0.4514632225036621</v>
+        <v>0.4439890682697296</v>
       </c>
       <c r="X2" t="n">
-        <v>44190846</v>
+        <v>6312978</v>
       </c>
       <c r="Y2" t="n">
         <v>0</v>
@@ -742,46 +742,46 @@
         <v>0</v>
       </c>
       <c r="AE2" t="n">
-        <v>44190846</v>
+        <v>6312978</v>
       </c>
       <c r="AF2" t="n">
-        <v>33659447</v>
+        <v>4787035</v>
       </c>
       <c r="AG2" t="n">
-        <v>20826834</v>
+        <v>2990204</v>
       </c>
       <c r="AH2" t="n">
-        <v>5601637</v>
+        <v>802709</v>
       </c>
       <c r="AI2" t="n">
-        <v>413079</v>
+        <v>59088</v>
       </c>
       <c r="AJ2" t="n">
-        <v>3215114</v>
+        <v>460006</v>
       </c>
       <c r="AK2" t="n">
-        <v>1260508</v>
+        <v>180185</v>
       </c>
       <c r="AL2" t="n">
         <v>1</v>
       </c>
       <c r="AM2" t="n">
-        <v>0.9563413858413696</v>
+        <v>0.9555707573890686</v>
       </c>
       <c r="AN2" t="n">
-        <v>0.9113937020301819</v>
+        <v>0.9118538498878479</v>
       </c>
       <c r="AO2" t="n">
-        <v>0.8582093119621277</v>
+        <v>0.8584820032119751</v>
       </c>
       <c r="AP2" t="n">
-        <v>0.6620789766311646</v>
+        <v>0.6613538861274719</v>
       </c>
       <c r="AQ2" t="n">
-        <v>0.9020217657089233</v>
+        <v>0.9020804166793823</v>
       </c>
       <c r="AR2" t="n">
-        <v>0.931441068649292</v>
+        <v>0.9314774870872498</v>
       </c>
     </row>
     <row r="3">
@@ -792,130 +792,130 @@
         <v>0.00202340465893989</v>
       </c>
       <c r="C3" t="n">
-        <v>416</v>
+        <v>61</v>
       </c>
       <c r="D3" t="n">
-        <v>29091054</v>
+        <v>4163752</v>
       </c>
       <c r="E3" t="n">
-        <v>5760787</v>
+        <v>794761</v>
       </c>
       <c r="F3" t="n">
-        <v>248753</v>
+        <v>34108</v>
       </c>
       <c r="G3" t="n">
-        <v>27497</v>
+        <v>3719</v>
       </c>
       <c r="H3" t="n">
-        <v>21789</v>
+        <v>2619</v>
       </c>
       <c r="I3" t="n">
-        <v>993</v>
+        <v>121</v>
       </c>
       <c r="J3" t="n">
-        <v>70112698</v>
+        <v>10016304</v>
       </c>
       <c r="K3" t="n">
-        <v>67624628</v>
+        <v>9639850</v>
       </c>
       <c r="L3" t="n">
-        <v>81924281</v>
+        <v>11713910</v>
       </c>
       <c r="M3" t="n">
-        <v>104774500</v>
+        <v>14964603</v>
       </c>
       <c r="N3" t="n">
-        <v>112742360</v>
+        <v>16107199</v>
       </c>
       <c r="O3" t="n">
-        <v>108949969</v>
+        <v>15569375</v>
       </c>
       <c r="P3" t="n">
-        <v>112925889</v>
+        <v>16132837</v>
       </c>
       <c r="Q3" t="n">
         <v>1</v>
       </c>
       <c r="R3" t="n">
-        <v>0.8275956511497498</v>
+        <v>0.8328934907913208</v>
       </c>
       <c r="S3" t="n">
-        <v>0.4778017997741699</v>
+        <v>0.4707480072975159</v>
       </c>
       <c r="T3" t="n">
-        <v>0.3091568648815155</v>
+        <v>0.3117647767066956</v>
       </c>
       <c r="U3" t="n">
-        <v>0.07136943191289902</v>
+        <v>0.07097826898097992</v>
       </c>
       <c r="V3" t="n">
-        <v>0.3402473330497742</v>
+        <v>0.3346550762653351</v>
       </c>
       <c r="W3" t="n">
-        <v>0.0168913621455431</v>
+        <v>0.01343620661646128</v>
       </c>
       <c r="X3" t="n">
         <v>0</v>
       </c>
       <c r="Y3" t="n">
-        <v>33659447</v>
+        <v>4787035</v>
       </c>
       <c r="Z3" t="n">
-        <v>1384204</v>
+        <v>196812</v>
       </c>
       <c r="AA3" t="n">
-        <v>59560</v>
+        <v>8425</v>
       </c>
       <c r="AB3" t="n">
-        <v>47621</v>
+        <v>6828</v>
       </c>
       <c r="AC3" t="n">
-        <v>247</v>
+        <v>11</v>
       </c>
       <c r="AD3" t="n">
-        <v>210</v>
+        <v>30</v>
       </c>
       <c r="AE3" t="n">
-        <v>70116354</v>
+        <v>10016622</v>
       </c>
       <c r="AF3" t="n">
-        <v>77619300</v>
+        <v>11107886</v>
       </c>
       <c r="AG3" t="n">
-        <v>89394449</v>
+        <v>12753027</v>
       </c>
       <c r="AH3" t="n">
-        <v>106848837</v>
+        <v>15260727</v>
       </c>
       <c r="AI3" t="n">
-        <v>113471912</v>
+        <v>16209880</v>
       </c>
       <c r="AJ3" t="n">
-        <v>110391725</v>
+        <v>15769225</v>
       </c>
       <c r="AK3" t="n">
-        <v>112860888</v>
+        <v>16122838</v>
       </c>
       <c r="AL3" t="n">
         <v>1</v>
       </c>
       <c r="AM3" t="n">
-        <v>0.9575594067573547</v>
+        <v>0.9575715065002441</v>
       </c>
       <c r="AN3" t="n">
-        <v>0.9099474549293518</v>
+        <v>0.9095625281333923</v>
       </c>
       <c r="AO3" t="n">
-        <v>0.8574531674385071</v>
+        <v>0.8570923805236816</v>
       </c>
       <c r="AP3" t="n">
-        <v>0.6615032553672791</v>
+        <v>0.6604667901992798</v>
       </c>
       <c r="AQ3" t="n">
-        <v>0.9015399217605591</v>
+        <v>0.9011915326118469</v>
       </c>
       <c r="AR3" t="n">
-        <v>0.9312731623649597</v>
+        <v>0.9311549663543701</v>
       </c>
     </row>
     <row r="4">
@@ -926,285 +926,285 @@
         <v>0.03193072151668488</v>
       </c>
       <c r="C4" t="n">
-        <v>177</v>
+        <v>29</v>
       </c>
       <c r="D4" t="n">
-        <v>10240101</v>
+        <v>1500450</v>
       </c>
       <c r="E4" t="n">
-        <v>10935905</v>
+        <v>1547593</v>
       </c>
       <c r="F4" t="n">
-        <v>1333117</v>
+        <v>187951</v>
       </c>
       <c r="G4" t="n">
-        <v>150766</v>
+        <v>20845</v>
       </c>
       <c r="H4" t="n">
-        <v>224026</v>
+        <v>30204</v>
       </c>
       <c r="I4" t="n">
-        <v>3861</v>
+        <v>447</v>
       </c>
       <c r="J4" t="n">
-        <v>3656</v>
+        <v>318</v>
       </c>
       <c r="K4" t="n">
-        <v>11531283</v>
+        <v>1690609</v>
       </c>
       <c r="L4" t="n">
-        <v>9494966</v>
+        <v>1328171</v>
       </c>
       <c r="M4" t="n">
-        <v>2999822</v>
+        <v>428448</v>
       </c>
       <c r="N4" t="n">
-        <v>940385</v>
+        <v>132937</v>
       </c>
       <c r="O4" t="n">
-        <v>1790984</v>
+        <v>249783</v>
       </c>
       <c r="P4" t="n">
-        <v>27779</v>
+        <v>3256</v>
       </c>
       <c r="Q4" t="n">
-        <v>0.9999586343765259</v>
+        <v>0.99997478723526</v>
       </c>
       <c r="R4" t="n">
-        <v>0.7678411602973938</v>
+        <v>0.7672642469406128</v>
       </c>
       <c r="S4" t="n">
-        <v>0.5049031376838684</v>
+        <v>0.5021975636482239</v>
       </c>
       <c r="T4" t="n">
-        <v>0.3496566712856293</v>
+        <v>0.3524278700351715</v>
       </c>
       <c r="U4" t="n">
-        <v>0.05538313463330269</v>
+        <v>0.05551888421177864</v>
       </c>
       <c r="V4" t="n">
-        <v>0.3693419396877289</v>
+        <v>0.3669460415840149</v>
       </c>
       <c r="W4" t="n">
-        <v>0.03256433829665184</v>
+        <v>0.02608307637274265</v>
       </c>
       <c r="X4" t="n">
         <v>0</v>
       </c>
       <c r="Y4" t="n">
-        <v>1434717</v>
+        <v>207948</v>
       </c>
       <c r="Z4" t="n">
-        <v>20826834</v>
+        <v>2990204</v>
       </c>
       <c r="AA4" t="n">
-        <v>579437</v>
+        <v>82633</v>
       </c>
       <c r="AB4" t="n">
-        <v>38501</v>
+        <v>5536</v>
       </c>
       <c r="AC4" t="n">
-        <v>7988</v>
+        <v>1130</v>
       </c>
       <c r="AD4" t="n">
-        <v>476</v>
+        <v>68</v>
       </c>
       <c r="AE4" t="n">
         <v>0</v>
       </c>
       <c r="AF4" t="n">
-        <v>1536611</v>
+        <v>222573</v>
       </c>
       <c r="AG4" t="n">
-        <v>2024798</v>
+        <v>289054</v>
       </c>
       <c r="AH4" t="n">
-        <v>925485</v>
+        <v>132324</v>
       </c>
       <c r="AI4" t="n">
-        <v>210833</v>
+        <v>30256</v>
       </c>
       <c r="AJ4" t="n">
-        <v>349228</v>
+        <v>49933</v>
       </c>
       <c r="AK4" t="n">
-        <v>92780</v>
+        <v>13255</v>
       </c>
       <c r="AL4" t="n">
         <v>1</v>
       </c>
       <c r="AM4" t="n">
-        <v>0.9569499492645264</v>
+        <v>0.9565700888633728</v>
       </c>
       <c r="AN4" t="n">
-        <v>0.9106699824333191</v>
+        <v>0.9107067584991455</v>
       </c>
       <c r="AO4" t="n">
-        <v>0.8578310608863831</v>
+        <v>0.8577865958213806</v>
       </c>
       <c r="AP4" t="n">
-        <v>0.6617910265922546</v>
+        <v>0.6609100103378296</v>
       </c>
       <c r="AQ4" t="n">
-        <v>0.9017807841300964</v>
+        <v>0.9016357064247131</v>
       </c>
       <c r="AR4" t="n">
-        <v>0.9313570857048035</v>
+        <v>0.9313161373138428</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr"/>
       <c r="B5" t="inlineStr"/>
       <c r="C5" t="n">
-        <v>476</v>
+        <v>49</v>
       </c>
       <c r="D5" t="n">
-        <v>955358</v>
+        <v>140818</v>
       </c>
       <c r="E5" t="n">
-        <v>2763288</v>
+        <v>393518</v>
       </c>
       <c r="F5" t="n">
-        <v>2019684</v>
+        <v>291983</v>
       </c>
       <c r="G5" t="n">
-        <v>243816</v>
+        <v>34539</v>
       </c>
       <c r="H5" t="n">
-        <v>543508</v>
+        <v>74842</v>
       </c>
       <c r="I5" t="n">
-        <v>6748</v>
+        <v>800</v>
       </c>
       <c r="J5" t="n">
         <v>0</v>
       </c>
       <c r="K5" t="n">
-        <v>6060235</v>
+        <v>835389</v>
       </c>
       <c r="L5" t="n">
-        <v>11952048</v>
+        <v>1739926</v>
       </c>
       <c r="M5" t="n">
-        <v>4513194</v>
+        <v>644566</v>
       </c>
       <c r="N5" t="n">
-        <v>579888</v>
+        <v>83114</v>
       </c>
       <c r="O5" t="n">
-        <v>2352841</v>
+        <v>339620</v>
       </c>
       <c r="P5" t="n">
-        <v>1330669</v>
+        <v>190907</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.9999679923057556</v>
+        <v>0.9999805092811584</v>
       </c>
       <c r="R5" t="n">
-        <v>0.8461031317710876</v>
+        <v>0.84531170129776</v>
       </c>
       <c r="S5" t="n">
-        <v>0.8123738765716553</v>
+        <v>0.8121143579483032</v>
       </c>
       <c r="T5" t="n">
-        <v>0.9342734813690186</v>
+        <v>0.9342902302742004</v>
       </c>
       <c r="U5" t="n">
-        <v>0.9867001175880432</v>
+        <v>0.9867693781852722</v>
       </c>
       <c r="V5" t="n">
-        <v>0.9637483358383179</v>
+        <v>0.9639058709144592</v>
       </c>
       <c r="W5" t="n">
-        <v>0.9881157875061035</v>
+        <v>0.9881097674369812</v>
       </c>
       <c r="X5" t="n">
         <v>0</v>
       </c>
       <c r="Y5" t="n">
-        <v>56186</v>
+        <v>8031</v>
       </c>
       <c r="Z5" t="n">
-        <v>596891</v>
+        <v>86001</v>
       </c>
       <c r="AA5" t="n">
-        <v>5601637</v>
+        <v>802709</v>
       </c>
       <c r="AB5" t="n">
-        <v>69704</v>
+        <v>9990</v>
       </c>
       <c r="AC5" t="n">
-        <v>204029</v>
+        <v>29185</v>
       </c>
       <c r="AD5" t="n">
-        <v>4431</v>
+        <v>633</v>
       </c>
       <c r="AE5" t="n">
         <v>0</v>
       </c>
       <c r="AF5" t="n">
-        <v>1491842</v>
+        <v>212106</v>
       </c>
       <c r="AG5" t="n">
-        <v>2061119</v>
+        <v>297315</v>
       </c>
       <c r="AH5" t="n">
-        <v>931241</v>
+        <v>133840</v>
       </c>
       <c r="AI5" t="n">
-        <v>211376</v>
+        <v>30376</v>
       </c>
       <c r="AJ5" t="n">
-        <v>351133</v>
+        <v>50436</v>
       </c>
       <c r="AK5" t="n">
-        <v>93024</v>
+        <v>13322</v>
       </c>
       <c r="AL5" t="n">
         <v>1</v>
       </c>
       <c r="AM5" t="n">
-        <v>0.9735060334205627</v>
+        <v>0.9733809232711792</v>
       </c>
       <c r="AN5" t="n">
-        <v>0.9642549753189087</v>
+        <v>0.9640916585922241</v>
       </c>
       <c r="AO5" t="n">
-        <v>0.9837567210197449</v>
+        <v>0.9837005138397217</v>
       </c>
       <c r="AP5" t="n">
-        <v>0.9963063597679138</v>
+        <v>0.9962869882583618</v>
       </c>
       <c r="AQ5" t="n">
-        <v>0.9938730001449585</v>
+        <v>0.9938535690307617</v>
       </c>
       <c r="AR5" t="n">
-        <v>0.9983745217323303</v>
+        <v>0.9983724355697632</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr"/>
       <c r="B6" t="inlineStr"/>
       <c r="C6" t="n">
-        <v>293</v>
+        <v>29</v>
       </c>
       <c r="D6" t="n">
-        <v>170779</v>
+        <v>25242</v>
       </c>
       <c r="E6" t="n">
-        <v>182155</v>
+        <v>25727</v>
       </c>
       <c r="F6" t="n">
-        <v>167818</v>
+        <v>24065</v>
       </c>
       <c r="G6" t="n">
-        <v>44567</v>
+        <v>6350</v>
       </c>
       <c r="H6" t="n">
-        <v>57242</v>
+        <v>7868</v>
       </c>
       <c r="I6" t="n">
-        <v>1601</v>
+        <v>183</v>
       </c>
       <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr"/>
@@ -1224,22 +1224,22 @@
         <v>0</v>
       </c>
       <c r="Y6" t="n">
-        <v>45337</v>
+        <v>6558</v>
       </c>
       <c r="Z6" t="n">
-        <v>37466</v>
+        <v>5350</v>
       </c>
       <c r="AA6" t="n">
-        <v>76329</v>
+        <v>10994</v>
       </c>
       <c r="AB6" t="n">
-        <v>413079</v>
+        <v>59088</v>
       </c>
       <c r="AC6" t="n">
-        <v>48877</v>
+        <v>6993</v>
       </c>
       <c r="AD6" t="n">
-        <v>3367</v>
+        <v>481</v>
       </c>
       <c r="AE6" t="inlineStr"/>
       <c r="AF6" t="inlineStr"/>
@@ -1260,25 +1260,25 @@
       <c r="A7" t="inlineStr"/>
       <c r="B7" t="inlineStr"/>
       <c r="C7" t="n">
-        <v>1042</v>
+        <v>65</v>
       </c>
       <c r="D7" t="n">
-        <v>150765</v>
+        <v>21977</v>
       </c>
       <c r="E7" t="n">
-        <v>700983</v>
+        <v>101116</v>
       </c>
       <c r="F7" t="n">
-        <v>1067923</v>
+        <v>155686</v>
       </c>
       <c r="G7" t="n">
-        <v>417552</v>
+        <v>59071</v>
       </c>
       <c r="H7" t="n">
-        <v>1213406</v>
+        <v>170822</v>
       </c>
       <c r="I7" t="n">
-        <v>14576</v>
+        <v>1705</v>
       </c>
       <c r="J7" t="inlineStr"/>
       <c r="K7" t="inlineStr"/>
@@ -1298,22 +1298,22 @@
         <v>0</v>
       </c>
       <c r="Y7" t="n">
-        <v>175</v>
+        <v>8</v>
       </c>
       <c r="Z7" t="n">
-        <v>5670</v>
+        <v>810</v>
       </c>
       <c r="AA7" t="n">
-        <v>207844</v>
+        <v>29939</v>
       </c>
       <c r="AB7" t="n">
-        <v>53148</v>
+        <v>7636</v>
       </c>
       <c r="AC7" t="n">
-        <v>3215114</v>
+        <v>460006</v>
       </c>
       <c r="AD7" t="n">
-        <v>84296</v>
+        <v>12043</v>
       </c>
       <c r="AE7" t="inlineStr"/>
       <c r="AF7" t="inlineStr"/>
@@ -1334,25 +1334,25 @@
       <c r="A8" t="inlineStr"/>
       <c r="B8" t="inlineStr"/>
       <c r="C8" t="n">
-        <v>1252</v>
+        <v>85</v>
       </c>
       <c r="D8" t="n">
-        <v>14280</v>
+        <v>2122</v>
       </c>
       <c r="E8" t="n">
-        <v>87753</v>
+        <v>13049</v>
       </c>
       <c r="F8" t="n">
-        <v>182211</v>
+        <v>26638</v>
       </c>
       <c r="G8" t="n">
-        <v>100754</v>
+        <v>14763</v>
       </c>
       <c r="H8" t="n">
-        <v>944419</v>
+        <v>134250</v>
       </c>
       <c r="I8" t="n">
-        <v>22863</v>
+        <v>2600</v>
       </c>
       <c r="J8" t="inlineStr"/>
       <c r="K8" t="inlineStr"/>
@@ -1372,22 +1372,22 @@
         <v>0</v>
       </c>
       <c r="Y8" t="n">
-        <v>196</v>
+        <v>28</v>
       </c>
       <c r="Z8" t="n">
-        <v>567</v>
+        <v>81</v>
       </c>
       <c r="AA8" t="n">
-        <v>2315</v>
+        <v>333</v>
       </c>
       <c r="AB8" t="n">
-        <v>1859</v>
+        <v>266</v>
       </c>
       <c r="AC8" t="n">
-        <v>88087</v>
+        <v>12614</v>
       </c>
       <c r="AD8" t="n">
-        <v>1260508</v>
+        <v>180185</v>
       </c>
       <c r="AE8" t="inlineStr"/>
       <c r="AF8" t="inlineStr"/>
